--- a/public/static/srzt.xlsx
+++ b/public/static/srzt.xlsx
@@ -1,14 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1桌面\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9060" firstSheet="4" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="venues" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="vetm" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="town" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="role" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="info" sheetId="5" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="梧田街道">vetm!$B$2:$AA$2</definedName>
+    <definedName name="茶山街道">vetm!$B$4:$Q$4</definedName>
+    <definedName name="景山街道">vetm!$B$1:$P$1</definedName>
+    <definedName name="南白象街道">vetm!$B$3:$P$3</definedName>
+    <definedName name="娄桥街道">vetm!$B$5:$K$5</definedName>
+    <definedName name="新桥街道">vetm!$B$6:$O$6</definedName>
+    <definedName name="三垟街道">vetm!$B$7:$N$7</definedName>
+    <definedName name="瞿溪街道">vetm!$B$8:$Q$8</definedName>
+    <definedName name="郭溪街道">vetm!$B$9:$Q$9</definedName>
+    <definedName name="潘桥街道">vetm!$B$10:$AB$10</definedName>
+    <definedName name="丽岙街道">vetm!$B$11:$Q$11</definedName>
+    <definedName name="仙岩街道">vetm!$B$12:$AE$12</definedName>
+    <definedName name="泽雅镇">vetm!$B$13:$BK$13</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,35 +51,1690 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="557">
+  <si>
+    <t>护国寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区景山街道护国寺</t>
+  </si>
+  <si>
+    <t>地藏王殿</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区西山东路118号</t>
+  </si>
+  <si>
+    <t>宝严寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区茶山街道徐岙村</t>
+  </si>
+  <si>
+    <t>茶山基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区茶山街道洞桥南路202号</t>
+  </si>
+  <si>
+    <t>大庆寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区茶山街道五美路</t>
+  </si>
+  <si>
+    <t>洪崖道观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区茶山街道洪殿村岩头</t>
+  </si>
+  <si>
+    <t>觉海寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区茶山街道罗山村</t>
+  </si>
+  <si>
+    <t>京山基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区茶山街道京山村</t>
+  </si>
+  <si>
+    <t>睦州垟基督教聚会点</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区茶山街道睦州垟新州路9号</t>
+  </si>
+  <si>
+    <t>山根基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区茶山街道山根村山根南路93号</t>
+  </si>
+  <si>
+    <t>实际寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区茶山街道罗丰村</t>
+  </si>
+  <si>
+    <t>汀岙基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区茶山街道汀岙路86号</t>
+  </si>
+  <si>
+    <t>卧云寺(罗丰)</t>
+  </si>
+  <si>
+    <t>下坦平基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区茶山街道新民村下坦平</t>
+  </si>
+  <si>
+    <t>香山寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区茶山街道罗胜村</t>
+  </si>
+  <si>
+    <t>心安禅寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区茶山街道新民村</t>
+  </si>
+  <si>
+    <t>延寿寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区茶山街道后村金沙路</t>
+  </si>
+  <si>
+    <t>杨溪寺</t>
+  </si>
+  <si>
+    <t>笔架山道观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区郭溪街道笔架山下</t>
+  </si>
+  <si>
+    <t>曹埭基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区郭溪街道凰桥村燎原中路226-228号</t>
+  </si>
+  <si>
+    <t>郭西基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区郭溪街道郭西村溪源路41弄12号</t>
+  </si>
+  <si>
+    <t>郭溪基督教聚会点</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区郭溪街道郭溪村</t>
+  </si>
+  <si>
+    <t>郭溪基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区郭溪街道河头村</t>
+  </si>
+  <si>
+    <t>黄桥基督教聚会点</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区郭溪街道黄桥村燎原中路170号</t>
+  </si>
+  <si>
+    <t>江垟新村基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区郭溪街道五和路80弄7幢73号</t>
+  </si>
+  <si>
+    <t>能仁寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区郭溪街道渚浦西村</t>
+  </si>
+  <si>
+    <t>浦东基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区郭溪街道浦东村</t>
+  </si>
+  <si>
+    <t>普宁寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区郭溪街道任桥村</t>
+  </si>
+  <si>
+    <t>庆全寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区郭溪街道梅园村</t>
+  </si>
+  <si>
+    <t>任相公观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区郭溪街道塘下梅园村</t>
+  </si>
+  <si>
+    <t>宋岙底基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区郭溪街道宋岙底村</t>
+  </si>
+  <si>
+    <t>塘下基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区郭溪街道温瞿东路1940号</t>
+  </si>
+  <si>
+    <t>塘下天主教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区郭溪街道塘下上村</t>
+  </si>
+  <si>
+    <t>陶湾基督教堂</t>
+  </si>
+  <si>
+    <t>苍峰宫</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区景山街道西山西路外莲花山</t>
+  </si>
+  <si>
+    <t>法果寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区景山街道西山东路102-1号</t>
+  </si>
+  <si>
+    <t>华光观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区景山街道西山东路102弄1号</t>
+  </si>
+  <si>
+    <t>金莲道观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区景山街道</t>
+  </si>
+  <si>
+    <t>净法寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区景山街道西山东路22弄2号</t>
+  </si>
+  <si>
+    <t>净社寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区景山街道雪山路153弄74号</t>
+  </si>
+  <si>
+    <t>净水寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区景山街道净水村</t>
+  </si>
+  <si>
+    <t>青莲禅寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区景山街道雪山饭店后面</t>
+  </si>
+  <si>
+    <t>太清宫</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区景山街道西山东路116号</t>
+  </si>
+  <si>
+    <t>乌岩道院</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区景山街道将军村乌岩头8号</t>
+  </si>
+  <si>
+    <t>显惠宫</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区景山街道净水村西山东路200弄内</t>
+  </si>
+  <si>
+    <t>玉鹿寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区景山街道西山西路二弄永康巷34号</t>
+  </si>
+  <si>
+    <t>白门基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区丽岙街道曹建村上横路坟亭山脚</t>
+  </si>
+  <si>
+    <t>白门心安寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区丽岙街道曹建村上横路和尚山脚</t>
+  </si>
+  <si>
+    <t>茶堂基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区丽岙街道茶堂村头潭巷10号</t>
+  </si>
+  <si>
+    <t>崇福观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区丽岙街道丽塘村东村</t>
+  </si>
+  <si>
+    <t>化成寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区丽岙街道上金村</t>
+  </si>
+  <si>
+    <t>丽塘基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区丽岙街道丽岙西路18号</t>
+  </si>
+  <si>
+    <t>普照寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区丽岙街道叶宅村</t>
+  </si>
+  <si>
+    <t>善隐寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区丽岙街道泊岙村</t>
+  </si>
+  <si>
+    <t>尚善寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区丽岙街道下呈村(尚善寺)</t>
+  </si>
+  <si>
+    <t>圣迹寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区丽岙街道姜宅村</t>
+  </si>
+  <si>
+    <t>水陆寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区丽岙街道杨宅村</t>
+  </si>
+  <si>
+    <t>下呈天主教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区丽岙街道下呈村(下呈天主教堂)</t>
+  </si>
+  <si>
+    <t>下川基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区丽岙街道下川村湖滨路6弄32号</t>
+  </si>
+  <si>
+    <t>杨圣观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区丽岙街道杨宅村芙蓉尖高峰</t>
+  </si>
+  <si>
+    <t>永宁寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区丽岙街道下章村</t>
+  </si>
+  <si>
+    <t>圆通堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区丽岙街道五社村</t>
+  </si>
+  <si>
+    <t>崇福寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区娄桥街道玕屿村</t>
+  </si>
+  <si>
+    <t>玕屿基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区娄桥街道玕屿南村</t>
+  </si>
+  <si>
+    <t>古岸头基督教聚会点</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区娄桥街道古岸头村</t>
+  </si>
+  <si>
+    <t>河庄基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区娄桥街道河庄村大埠头</t>
+  </si>
+  <si>
+    <t>寂光寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区娄桥街道安下村</t>
+  </si>
+  <si>
+    <t>娄桥基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区娄桥街道娄社路6号</t>
+  </si>
+  <si>
+    <t>弥陀精舍</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区娄桥街道前园村</t>
+  </si>
+  <si>
+    <t>南山基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区娄桥街道东风东新街20弄23号</t>
+  </si>
+  <si>
+    <t>无量道观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区娄桥街道东耕村吹台山</t>
+  </si>
+  <si>
+    <t>云会寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区娄桥街道前村桃源路</t>
+  </si>
+  <si>
+    <t>白象基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区南白象街道凤凰路32号</t>
+  </si>
+  <si>
+    <t>白云道观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区南白象街道白象村寺前路1号</t>
+  </si>
+  <si>
+    <t>宝筏寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区南白象街道上蔡村</t>
+  </si>
+  <si>
+    <t>东庄基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区南白象街道东庄村60号</t>
+  </si>
+  <si>
+    <t>洞文观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区南白象街道白象村</t>
+  </si>
+  <si>
+    <t>鹅湖基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区南白象街道鹅湖村鹅湖西路30号</t>
+  </si>
+  <si>
+    <t>木角桥基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区南白象街道霞坊村木角桥1号</t>
+  </si>
+  <si>
+    <t>南湖基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区南白象街道南湖北路61号</t>
+  </si>
+  <si>
+    <t>前林大圣观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区南白象街道前林</t>
+  </si>
+  <si>
+    <t>桥头河基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区南白象街道上蔡村桥头河</t>
+  </si>
+  <si>
+    <t>清凉道观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区南白象街道南湖村陈庄</t>
+  </si>
+  <si>
+    <t>上蔡基督教堂</t>
+  </si>
+  <si>
+    <t>霞坊嶂屿山观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区南白象街道霞坊嶂屿山</t>
+  </si>
+  <si>
+    <t>永福禅寺</t>
+  </si>
+  <si>
+    <t>碧云寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道横塘村</t>
+  </si>
+  <si>
+    <t>陈岙基督教堂(潘桥)</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道陈岙溪下路38号</t>
+  </si>
+  <si>
+    <t>陈龙观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道陈庄村</t>
+  </si>
+  <si>
+    <t>陈庄基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道陈庄村前岸路45号</t>
+  </si>
+  <si>
+    <t>福源寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道丁岙村</t>
+  </si>
+  <si>
+    <t>横塘基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道横塘村永泰路14号</t>
+  </si>
+  <si>
+    <t>集福寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道屏山村上岙底屏山西街49号</t>
+  </si>
+  <si>
+    <t>金堡基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道金堡村</t>
+  </si>
+  <si>
+    <t>金堡天主教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道永生路1号</t>
+  </si>
+  <si>
+    <t>老竹基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道东边村新桐路1386号</t>
+  </si>
+  <si>
+    <t>林竹庵</t>
+  </si>
+  <si>
+    <t>马桥基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道马桥村马桥头</t>
+  </si>
+  <si>
+    <t>马桥天主教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道马桥村</t>
+  </si>
+  <si>
+    <t>岷岗基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道岷岗新牧路72号</t>
+  </si>
+  <si>
+    <t>南泉寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道河西村</t>
+  </si>
+  <si>
+    <t>潘桥基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道林桥头村</t>
+  </si>
+  <si>
+    <t>屏山基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道屏山村</t>
+  </si>
+  <si>
+    <t>清福寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道屏山下岙村</t>
+  </si>
+  <si>
+    <t>上清观</t>
+  </si>
+  <si>
+    <t>天竺寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道焦下村</t>
+  </si>
+  <si>
+    <t>桐岭基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道桐岭村繁荣路10弄22号</t>
+  </si>
+  <si>
+    <t>五斗太阴宫</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道河西村皎庄</t>
+  </si>
+  <si>
+    <t>霞碧宫</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道霞碧山</t>
+  </si>
+  <si>
+    <t>仙门基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道仙门村</t>
+  </si>
+  <si>
+    <t>玉泉禅寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道丁岙村彭岙玉泉路51号</t>
+  </si>
+  <si>
+    <t>证圣禅寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道老竹村</t>
+  </si>
+  <si>
+    <t>忠义观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区潘桥街道林桥头东路29号</t>
+  </si>
+  <si>
+    <t>八仙岩道观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区瞿溪街道桥下村</t>
+  </si>
+  <si>
+    <t>大岙基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区瞿溪街道大岙村</t>
+  </si>
+  <si>
+    <t>大同村基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区瞿溪街道大同村</t>
+  </si>
+  <si>
+    <t>河头基督教堂(宁屿路)</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区瞿溪街道宁屿路104号</t>
+  </si>
+  <si>
+    <t>会善寺(瞿溪)</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区瞿溪街道瞿溪村</t>
+  </si>
+  <si>
+    <t>林桥基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区瞿溪街道林桥村</t>
+  </si>
+  <si>
+    <t>普明寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区瞿溪街道后屿街239号</t>
+  </si>
+  <si>
+    <t>桥上基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区瞿溪街道桥上村石柱门路3号</t>
+  </si>
+  <si>
+    <t>瞿岙基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区瞿溪街道瞿岙村金溪路102号</t>
+  </si>
+  <si>
+    <t>瞿溪基督教聚会点</t>
+  </si>
+  <si>
+    <t>瞿溪基督教堂</t>
+  </si>
+  <si>
+    <t>瞿溪天主教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区瞿溪街道宁屿路221弄77号</t>
+  </si>
+  <si>
+    <t>泉东川基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区瞿溪街道泉东川村</t>
+  </si>
+  <si>
+    <t>沙对垟基督教聚会点</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区瞿溪街道桥上村沙对垟</t>
+  </si>
+  <si>
+    <t>雄溪基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区瞿溪街道雄溪村</t>
+  </si>
+  <si>
+    <t>肇山基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区瞿溪街道肇山村</t>
+  </si>
+  <si>
+    <t>河头基督教堂(垟河村)</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区三垟街道垟河村</t>
+  </si>
+  <si>
+    <t>黄屿基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区三垟街道黄屿村山前山上</t>
+  </si>
+  <si>
+    <t>黄屿天主教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区三垟街道黄屿沿河路95号</t>
+  </si>
+  <si>
+    <t>莲花堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区三垟街道园底村三茶路587号</t>
+  </si>
+  <si>
+    <t>榕源寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区三垟街道樟岙村</t>
+  </si>
+  <si>
+    <t>三垟基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区三垟街道后垟路20弄9号</t>
+  </si>
+  <si>
+    <t>沙滩头基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区三垟街道丹东村沙滩头路21弄25号</t>
+  </si>
+  <si>
+    <t>五灵观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区三垟街道吕家岸村兴岸路64号</t>
+  </si>
+  <si>
+    <t>夏家牌太阴宫</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区三垟街道夏家牌82号</t>
+  </si>
+  <si>
+    <t>仙平寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区三垟街道夏家牌</t>
+  </si>
+  <si>
+    <t>显政禅寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区三垟街道黄屿村寺前路1号</t>
+  </si>
+  <si>
+    <t>永丰桥基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区三垟街道吕家岸村永丰桥</t>
+  </si>
+  <si>
+    <t>张家桥太阴宫</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区三垟街道沙河村张家桥58号</t>
+  </si>
+  <si>
+    <t>伴云道观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道南村</t>
+  </si>
+  <si>
+    <t>北村基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道北村顺展路24号</t>
+  </si>
+  <si>
+    <t>慈航道院</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道南村幸福路81号</t>
+  </si>
+  <si>
+    <t>法通寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道慈湖北村慈湖路288号</t>
+  </si>
+  <si>
+    <t>福聚寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道河池路168号</t>
+  </si>
+  <si>
+    <t>横山宫</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区牛山南路底沙门</t>
+  </si>
+  <si>
+    <t>聚圣观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道梧三路227号</t>
+  </si>
+  <si>
+    <t>丽田基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道辽东村</t>
+  </si>
+  <si>
+    <t>丽田太阴宫</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道南丽田街32-34号</t>
+  </si>
+  <si>
+    <t>林村基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道林村村</t>
+  </si>
+  <si>
+    <t>林荫寺</t>
+  </si>
+  <si>
+    <t>妙鸿道院</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道塘西村殿后路2号</t>
+  </si>
+  <si>
+    <t>南堡寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道南堡村童宅巷68号</t>
+  </si>
+  <si>
+    <t>南村基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道南村村后巷13号</t>
+  </si>
+  <si>
+    <t>蟠凤基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道蟠凤村灯笼夹路1弄1号</t>
+  </si>
+  <si>
+    <t>普济寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道寮东村丽田街31号</t>
+  </si>
+  <si>
+    <t>沙门基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道沙门南路97号</t>
+  </si>
+  <si>
+    <t>沙门寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道沙门村</t>
+  </si>
+  <si>
+    <t>塘东基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道龙霞路420号</t>
+  </si>
+  <si>
+    <t>塘西陈圣观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道塘西山村咸占渎</t>
+  </si>
+  <si>
+    <t>梧田基督教聚会点</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道梧田街村东垟路</t>
+  </si>
+  <si>
+    <t>梧田基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道大堡底村</t>
+  </si>
+  <si>
+    <t>梧田太阴宫</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道东垟金川路</t>
+  </si>
+  <si>
+    <t>香城寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道老殿后村牛桥路</t>
+  </si>
+  <si>
+    <t>益寿堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区梧田街道蟠凤村</t>
+  </si>
+  <si>
+    <t>安福禅寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道穗丰村</t>
+  </si>
+  <si>
+    <t>白云寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道仙北村(白云寺)</t>
+  </si>
+  <si>
+    <t>宝岩寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道西一村大罗山</t>
+  </si>
+  <si>
+    <t>赤云寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道西二村</t>
+  </si>
+  <si>
+    <t>崇庆寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道竹溪村</t>
+  </si>
+  <si>
+    <t>慈宁宫</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道岩二村</t>
+  </si>
+  <si>
+    <t>伏虎寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道仙北村(伏虎寺)</t>
+  </si>
+  <si>
+    <t>甘露寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道河口塘村河滨中路7号</t>
+  </si>
+  <si>
+    <t>观音堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道社帆村</t>
+  </si>
+  <si>
+    <t>广福寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道沈岙村(广福寺)</t>
+  </si>
+  <si>
+    <t>河口塘基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道河口塘村</t>
+  </si>
+  <si>
+    <t>黄云寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道派岩西一村</t>
+  </si>
+  <si>
+    <t>会善寺(下林)</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道下林村(会善寺)</t>
+  </si>
+  <si>
+    <t>津延寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道岩二村朱繁路71号</t>
+  </si>
+  <si>
+    <t>罗隐寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道大罗山西一村</t>
+  </si>
+  <si>
+    <t>普善寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道沈岙村(普善寺)</t>
+  </si>
+  <si>
+    <t>庆云寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道自力村</t>
+  </si>
+  <si>
+    <t>社岙基督教堂</t>
+  </si>
+  <si>
+    <t>圣寿禅寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道仙北村(圣寿禅寺)</t>
+  </si>
+  <si>
+    <t>穗丰基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道穗丰村山前路10号</t>
+  </si>
+  <si>
+    <t>天护寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道仙南村</t>
+  </si>
+  <si>
+    <t>天庆寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道渔潭前村</t>
+  </si>
+  <si>
+    <t>下林基督教聚会点</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道下林村(下林基督教聚会点)</t>
+  </si>
+  <si>
+    <t>下林基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩镇下林村温霞南路</t>
+  </si>
+  <si>
+    <t>休凉寺</t>
+  </si>
+  <si>
+    <t>岩头寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道西一村</t>
+  </si>
+  <si>
+    <t>岩下基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道岩下村</t>
+  </si>
+  <si>
+    <t>永福寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道仙北村中北路9号</t>
+  </si>
+  <si>
+    <t>增福禅寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道星光村</t>
+  </si>
+  <si>
+    <t>增福寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区仙岩街道仙北村(增福寺)</t>
+  </si>
+  <si>
+    <t>宝界禅寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区新桥街道山前村</t>
+  </si>
+  <si>
+    <t>大悲寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区新桥街道山前村西岙底</t>
+  </si>
+  <si>
+    <t>高翔基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区新桥街道高翔牛山西路145号</t>
+  </si>
+  <si>
+    <t>鹤云观</t>
+  </si>
+  <si>
+    <t>礼慧讲寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区新桥街道高翔村牛山路15号</t>
+  </si>
+  <si>
+    <t>青心观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区新桥街道高翔村牛山路17号</t>
+  </si>
+  <si>
+    <t>卧云寺(阳岙)</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区新桥街道阳岙村</t>
+  </si>
+  <si>
+    <t>西堡基督教聚会点</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区新桥街道西堡西宁街10号</t>
+  </si>
+  <si>
+    <t>香积寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区新桥街道西山西路290弄</t>
+  </si>
+  <si>
+    <t>新桥基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区新桥街道西岸村</t>
+  </si>
+  <si>
+    <t>新桥天主教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区新桥街道西堡西宁后巷4号</t>
+  </si>
+  <si>
+    <t>阳岙基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区新桥街道东曹路55号</t>
+  </si>
+  <si>
+    <t>一心庵</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区新桥街道永庆街92弄5号</t>
+  </si>
+  <si>
+    <t>庄济观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区新桥街道山前社区</t>
+  </si>
+  <si>
+    <t>安乐溪基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇安乐溪村</t>
+  </si>
+  <si>
+    <t>坳头基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇隔岸村</t>
+  </si>
+  <si>
+    <t>包岙基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇包岙村</t>
+  </si>
+  <si>
+    <t>陈岙基督教堂(陈岙村)</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇陈岙村</t>
+  </si>
+  <si>
+    <t>陈垟宫</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇天长村</t>
+  </si>
+  <si>
+    <t>大石垟天主教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇大石垟村</t>
+  </si>
+  <si>
+    <t>东岸基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇李山村</t>
+  </si>
+  <si>
+    <t>戈恬基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇戈恬村大坟山山脚</t>
+  </si>
+  <si>
+    <t>戈恬天主教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇戈恬村</t>
+  </si>
+  <si>
+    <t>古双基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇古双村</t>
+  </si>
+  <si>
+    <t>桂川基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇桂川村</t>
+  </si>
+  <si>
+    <t>鹤岙基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇鹤岙村</t>
+  </si>
+  <si>
+    <t>黄公楼基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇山后村黄公楼</t>
+  </si>
+  <si>
+    <t>黄坑基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇黄坑村</t>
+  </si>
+  <si>
+    <t>黄岭头基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇黄岭头村</t>
+  </si>
+  <si>
+    <t>黄山基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇黄山村</t>
+  </si>
+  <si>
+    <t>寂照禅寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇大垟村</t>
+  </si>
+  <si>
+    <t>金岙基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇金岙村</t>
+  </si>
+  <si>
+    <t>进垟基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇进垟村</t>
+  </si>
+  <si>
+    <t>库门坳基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇库门坳村</t>
+  </si>
+  <si>
+    <t>林岙基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇林岙村</t>
+  </si>
+  <si>
+    <t>林垟基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇胡坦村</t>
+  </si>
+  <si>
+    <t>凌云寺</t>
+  </si>
+  <si>
+    <t>岭雪基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇岭雪村第二小组东路下</t>
+  </si>
+  <si>
+    <t>刘大宫</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇南山村</t>
+  </si>
+  <si>
+    <t>龙井宫</t>
+  </si>
+  <si>
+    <t>龙头基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇龙头村</t>
+  </si>
+  <si>
+    <t>龙头真武宫</t>
+  </si>
+  <si>
+    <t>路坳头基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇郑坑村路坳头</t>
+  </si>
+  <si>
+    <t>麻芝川基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇麻芝川村</t>
+  </si>
+  <si>
+    <t>庙后基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇庙后村</t>
+  </si>
+  <si>
+    <t>潘宅基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇潘宅村</t>
+  </si>
+  <si>
+    <t>三马路基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇仙宅山村</t>
+  </si>
+  <si>
+    <t>山后基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇并村垟村</t>
+  </si>
+  <si>
+    <t>上潘基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇上潘村</t>
+  </si>
+  <si>
+    <t>上潘镇武宫</t>
+  </si>
+  <si>
+    <t>石坑基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇石坑村</t>
+  </si>
+  <si>
+    <t>石马宫</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇下村大港头</t>
+  </si>
+  <si>
+    <t>石桥基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇石桥村</t>
+  </si>
+  <si>
+    <t>双一基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇双一村</t>
+  </si>
+  <si>
+    <t>唐口龙基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇唐口龙村</t>
+  </si>
+  <si>
+    <t>唐宅基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇唐宅村</t>
+  </si>
+  <si>
+    <t>天长基督教堂</t>
+  </si>
+  <si>
+    <t>外叶村基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇外叶村</t>
+  </si>
+  <si>
+    <t>五凤垟基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇五凤垟村</t>
+  </si>
+  <si>
+    <t>西岸基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇西岸村</t>
+  </si>
+  <si>
+    <t>西岸乡苏田基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇西岸乡苏田村</t>
+  </si>
+  <si>
+    <t>西雁基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇下庵村</t>
+  </si>
+  <si>
+    <t>下村基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇下村村</t>
+  </si>
+  <si>
+    <t>下连坑基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇下连坑村</t>
+  </si>
+  <si>
+    <t>下良基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇下良村</t>
+  </si>
+  <si>
+    <t>小石垟基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇小石垟村</t>
+  </si>
+  <si>
+    <t>小源基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇小源村</t>
+  </si>
+  <si>
+    <t>言章基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇言章村</t>
+  </si>
+  <si>
+    <t>岩角山基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇岩角山村</t>
+  </si>
+  <si>
+    <t>岩门基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇岩门村</t>
+  </si>
+  <si>
+    <t>岩头宫</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇李降垟村</t>
+  </si>
+  <si>
+    <t>垟坑基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇垟坑村</t>
+  </si>
+  <si>
+    <t>垟田基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇垟田村</t>
+  </si>
+  <si>
+    <t>屿山基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇屿山村</t>
+  </si>
+  <si>
+    <t>源口基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇源口村顺京路84号</t>
+  </si>
+  <si>
+    <t>郑家山基督教堂</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区泽雅镇郑家山村</t>
+  </si>
+  <si>
+    <t>平安寺（居士林）</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区慈湖平安路218号</t>
+  </si>
+  <si>
+    <t>紫霄道观</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区景山街道西山东路234弄</t>
+  </si>
+  <si>
+    <t>头陀寺</t>
+  </si>
+  <si>
+    <t>浙江省温州市瓯海区南白象街道鹅湖村</t>
+  </si>
+  <si>
+    <t>景山街道</t>
+  </si>
+  <si>
+    <t>梧田街道</t>
+  </si>
+  <si>
+    <t>南白象街道</t>
+  </si>
+  <si>
+    <t>茶山街道</t>
+  </si>
+  <si>
+    <t>娄桥街道</t>
+  </si>
+  <si>
+    <t>新桥街道</t>
+  </si>
+  <si>
+    <t>三垟街道</t>
+  </si>
+  <si>
+    <t>瞿溪街道</t>
+  </si>
+  <si>
+    <t>郭溪街道</t>
+  </si>
+  <si>
+    <t>潘桥街道</t>
+  </si>
+  <si>
+    <t>丽岙街道</t>
+  </si>
+  <si>
+    <t>仙岩街道</t>
+  </si>
+  <si>
+    <t>泽雅镇</t>
+  </si>
+  <si>
+    <t>组长</t>
+  </si>
+  <si>
+    <t>组员</t>
+  </si>
+  <si>
+    <t>角色编号</t>
+  </si>
+  <si>
+    <t>街道编号</t>
+  </si>
+  <si>
+    <t>场所编号</t>
+  </si>
   <si>
     <t>姓名</t>
   </si>
   <si>
+    <t>手机号码</t>
+  </si>
+  <si>
     <t>职务</t>
   </si>
   <si>
-    <t>驻堂场所编号</t>
-  </si>
-  <si>
-    <t>手机号码</t>
-  </si>
-  <si>
-    <t>组员</t>
+    <t>街道</t>
+  </si>
+  <si>
+    <t>场所</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,8 +1743,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="14"/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -536,159 +2229,169 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1016,7 +2719,7 @@
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
@@ -1051,7 +2754,7 @@
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
@@ -1215,42 +2918,5022 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="22" customHeight="1" outlineLevelRow="1" outlineLevelCol="3"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:D276"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="19" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.3333333333333" style="3" customWidth="1"/>
-    <col min="3" max="3" width="37.7777777777778" customWidth="1"/>
-    <col min="4" max="4" width="29.7777777777778" style="4" customWidth="1"/>
+    <col min="1" max="1" width="22.3333333333333" style="9" customWidth="1"/>
+    <col min="2" max="2" width="15.1111111111111" style="10" customWidth="1"/>
+    <col min="3" max="3" width="14.1111111111111" style="10" customWidth="1"/>
+    <col min="4" max="4" width="54" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="33" customHeight="1" spans="1:4">
+    <row r="1" spans="1:4">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10">
+        <v>10000001</v>
+      </c>
+      <c r="C1" s="10">
+        <v>330304001</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="10">
+        <v>10000002</v>
+      </c>
+      <c r="C2" s="10">
+        <v>330304001</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="10">
+        <v>10000003</v>
+      </c>
+      <c r="C3" s="10">
+        <v>330304004</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="10">
+        <v>10000004</v>
+      </c>
+      <c r="C4" s="10">
+        <v>330304004</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="10">
+        <v>10000005</v>
+      </c>
+      <c r="C5" s="10">
+        <v>330304004</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="10">
+        <v>10000006</v>
+      </c>
+      <c r="C6" s="10">
+        <v>330304004</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="10">
+        <v>10000007</v>
+      </c>
+      <c r="C7" s="10">
+        <v>330304004</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="10">
+        <v>10000008</v>
+      </c>
+      <c r="C8" s="10">
+        <v>330304004</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="10">
+        <v>10000009</v>
+      </c>
+      <c r="C9" s="10">
+        <v>330304004</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="10">
+        <v>10000010</v>
+      </c>
+      <c r="C10" s="10">
+        <v>330304004</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="10">
+        <v>10000011</v>
+      </c>
+      <c r="C11" s="10">
+        <v>330304004</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="10">
+        <v>10000012</v>
+      </c>
+      <c r="C12" s="10">
+        <v>330304004</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="10">
+        <v>10000013</v>
+      </c>
+      <c r="C13" s="10">
+        <v>330304004</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="10">
+        <v>10000014</v>
+      </c>
+      <c r="C14" s="10">
+        <v>330304004</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="10">
+        <v>10000015</v>
+      </c>
+      <c r="C15" s="10">
+        <v>330304004</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="10">
+        <v>10000016</v>
+      </c>
+      <c r="C16" s="10">
+        <v>330304004</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="10">
+        <v>10000017</v>
+      </c>
+      <c r="C17" s="10">
+        <v>330304004</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="10">
+        <v>10000018</v>
+      </c>
+      <c r="C18" s="10">
+        <v>330304004</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="10">
+        <v>10000019</v>
+      </c>
+      <c r="C19" s="10">
+        <v>330304009</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="10">
+        <v>10000020</v>
+      </c>
+      <c r="C20" s="10">
+        <v>330304009</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="10">
+        <v>10000021</v>
+      </c>
+      <c r="C21" s="10">
+        <v>330304009</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="10">
+        <v>10000022</v>
+      </c>
+      <c r="C22" s="10">
+        <v>330304009</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="10">
+        <v>10000023</v>
+      </c>
+      <c r="C23" s="10">
+        <v>330304009</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="10">
+        <v>10000024</v>
+      </c>
+      <c r="C24" s="10">
+        <v>330304009</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="10">
+        <v>10000025</v>
+      </c>
+      <c r="C25" s="10">
+        <v>330304009</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="10">
+        <v>10000026</v>
+      </c>
+      <c r="C26" s="10">
+        <v>330304009</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="10">
+        <v>10000027</v>
+      </c>
+      <c r="C27" s="10">
+        <v>330304009</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="10">
+        <v>10000028</v>
+      </c>
+      <c r="C28" s="10">
+        <v>330304009</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="10">
+        <v>10000029</v>
+      </c>
+      <c r="C29" s="10">
+        <v>330304009</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="10">
+        <v>10000030</v>
+      </c>
+      <c r="C30" s="10">
+        <v>330304009</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="10">
+        <v>10000031</v>
+      </c>
+      <c r="C31" s="10">
+        <v>330304009</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" s="10">
+        <v>10000032</v>
+      </c>
+      <c r="C32" s="10">
+        <v>330304009</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="10">
+        <v>10000033</v>
+      </c>
+      <c r="C33" s="10">
+        <v>330304009</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" s="10">
+        <v>10000034</v>
+      </c>
+      <c r="C34" s="10">
+        <v>330304009</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" s="10">
+        <v>10000035</v>
+      </c>
+      <c r="C35" s="10">
+        <v>330304001</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" s="10">
+        <v>10000036</v>
+      </c>
+      <c r="C36" s="10">
+        <v>330304001</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B37" s="10">
+        <v>10000037</v>
+      </c>
+      <c r="C37" s="10">
+        <v>330304001</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" s="10">
+        <v>10000038</v>
+      </c>
+      <c r="C38" s="10">
+        <v>330304001</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" s="10">
+        <v>10000039</v>
+      </c>
+      <c r="C39" s="10">
+        <v>330304001</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40" s="10">
+        <v>10000040</v>
+      </c>
+      <c r="C40" s="10">
+        <v>330304001</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B41" s="10">
+        <v>10000041</v>
+      </c>
+      <c r="C41" s="10">
+        <v>330304001</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B42" s="10">
+        <v>10000042</v>
+      </c>
+      <c r="C42" s="10">
+        <v>330304001</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B43" s="10">
+        <v>10000043</v>
+      </c>
+      <c r="C43" s="10">
+        <v>330304001</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B44" s="10">
+        <v>10000044</v>
+      </c>
+      <c r="C44" s="10">
+        <v>330304001</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B45" s="10">
+        <v>10000045</v>
+      </c>
+      <c r="C45" s="10">
+        <v>330304001</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B46" s="10">
+        <v>10000046</v>
+      </c>
+      <c r="C46" s="10">
+        <v>330304001</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B47" s="10">
+        <v>10000047</v>
+      </c>
+      <c r="C47" s="10">
+        <v>330304011</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B48" s="10">
+        <v>10000048</v>
+      </c>
+      <c r="C48" s="10">
+        <v>330304011</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B49" s="10">
+        <v>10000049</v>
+      </c>
+      <c r="C49" s="10">
+        <v>330304011</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B50" s="10">
+        <v>10000050</v>
+      </c>
+      <c r="C50" s="10">
+        <v>330304011</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B51" s="10">
+        <v>10000051</v>
+      </c>
+      <c r="C51" s="10">
+        <v>330304011</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B52" s="10">
+        <v>10000052</v>
+      </c>
+      <c r="C52" s="10">
+        <v>330304011</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B53" s="10">
+        <v>10000053</v>
+      </c>
+      <c r="C53" s="10">
+        <v>330304011</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B54" s="10">
+        <v>10000054</v>
+      </c>
+      <c r="C54" s="10">
+        <v>330304011</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B55" s="10">
+        <v>10000055</v>
+      </c>
+      <c r="C55" s="10">
+        <v>330304011</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B56" s="10">
+        <v>10000056</v>
+      </c>
+      <c r="C56" s="10">
+        <v>330304011</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B57" s="10">
+        <v>10000057</v>
+      </c>
+      <c r="C57" s="10">
+        <v>330304011</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B58" s="10">
+        <v>10000058</v>
+      </c>
+      <c r="C58" s="10">
+        <v>330304011</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B59" s="10">
+        <v>10000059</v>
+      </c>
+      <c r="C59" s="10">
+        <v>330304011</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B60" s="10">
+        <v>10000060</v>
+      </c>
+      <c r="C60" s="10">
+        <v>330304011</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B61" s="10">
+        <v>10000061</v>
+      </c>
+      <c r="C61" s="10">
+        <v>330304011</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B62" s="10">
+        <v>10000062</v>
+      </c>
+      <c r="C62" s="10">
+        <v>330304011</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B63" s="10">
+        <v>10000063</v>
+      </c>
+      <c r="C63" s="10">
+        <v>330304005</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B64" s="10">
+        <v>10000064</v>
+      </c>
+      <c r="C64" s="10">
+        <v>330304005</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B65" s="10">
+        <v>10000065</v>
+      </c>
+      <c r="C65" s="10">
+        <v>330304005</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B66" s="10">
+        <v>10000066</v>
+      </c>
+      <c r="C66" s="10">
+        <v>330304005</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B67" s="10">
+        <v>10000067</v>
+      </c>
+      <c r="C67" s="10">
+        <v>330304005</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B68" s="10">
+        <v>10000068</v>
+      </c>
+      <c r="C68" s="10">
+        <v>330304005</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B69" s="10">
+        <v>10000069</v>
+      </c>
+      <c r="C69" s="10">
+        <v>330304005</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B70" s="10">
+        <v>10000070</v>
+      </c>
+      <c r="C70" s="10">
+        <v>330304005</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B71" s="10">
+        <v>10000071</v>
+      </c>
+      <c r="C71" s="10">
+        <v>330304005</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B72" s="10">
+        <v>10000072</v>
+      </c>
+      <c r="C72" s="10">
+        <v>330304005</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="B73" s="10">
+        <v>10000073</v>
+      </c>
+      <c r="C73" s="10">
+        <v>330304003</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B74" s="10">
+        <v>10000074</v>
+      </c>
+      <c r="C74" s="10">
+        <v>330304003</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="B75" s="10">
+        <v>10000075</v>
+      </c>
+      <c r="C75" s="10">
+        <v>330304003</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B76" s="10">
+        <v>10000076</v>
+      </c>
+      <c r="C76" s="10">
+        <v>330304003</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B77" s="10">
+        <v>10000077</v>
+      </c>
+      <c r="C77" s="10">
+        <v>330304003</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="B78" s="10">
+        <v>10000078</v>
+      </c>
+      <c r="C78" s="10">
+        <v>330304003</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B79" s="10">
+        <v>10000079</v>
+      </c>
+      <c r="C79" s="10">
+        <v>330304003</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="B80" s="10">
+        <v>10000080</v>
+      </c>
+      <c r="C80" s="10">
+        <v>330304003</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B81" s="10">
+        <v>10000081</v>
+      </c>
+      <c r="C81" s="10">
+        <v>330304003</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B82" s="10">
+        <v>10000082</v>
+      </c>
+      <c r="C82" s="10">
+        <v>330304003</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B83" s="10">
+        <v>10000083</v>
+      </c>
+      <c r="C83" s="10">
+        <v>330304003</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B84" s="10">
+        <v>10000084</v>
+      </c>
+      <c r="C84" s="10">
+        <v>330304003</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B85" s="10">
+        <v>10000085</v>
+      </c>
+      <c r="C85" s="10">
+        <v>330304003</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="B86" s="10">
+        <v>10000086</v>
+      </c>
+      <c r="C86" s="10">
+        <v>330304003</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B87" s="10">
+        <v>10000087</v>
+      </c>
+      <c r="C87" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="B88" s="10">
+        <v>10000088</v>
+      </c>
+      <c r="C88" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="B89" s="10">
+        <v>10000089</v>
+      </c>
+      <c r="C89" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B90" s="10">
+        <v>10000090</v>
+      </c>
+      <c r="C90" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B91" s="10">
+        <v>10000091</v>
+      </c>
+      <c r="C91" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B92" s="10">
+        <v>10000092</v>
+      </c>
+      <c r="C92" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="B93" s="10">
+        <v>10000093</v>
+      </c>
+      <c r="C93" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B94" s="10">
+        <v>10000094</v>
+      </c>
+      <c r="C94" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="B95" s="10">
+        <v>10000095</v>
+      </c>
+      <c r="C95" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B96" s="10">
+        <v>10000096</v>
+      </c>
+      <c r="C96" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B97" s="10">
+        <v>10000097</v>
+      </c>
+      <c r="C97" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B98" s="10">
+        <v>10000098</v>
+      </c>
+      <c r="C98" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="B99" s="10">
+        <v>10000099</v>
+      </c>
+      <c r="C99" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="B100" s="10">
+        <v>10000100</v>
+      </c>
+      <c r="C100" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B101" s="10">
+        <v>10000101</v>
+      </c>
+      <c r="C101" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="B102" s="10">
+        <v>10000102</v>
+      </c>
+      <c r="C102" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D102" s="9" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B103" s="10">
+        <v>10000103</v>
+      </c>
+      <c r="C103" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="B104" s="10">
+        <v>10000104</v>
+      </c>
+      <c r="C104" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="B105" s="10">
+        <v>10000105</v>
+      </c>
+      <c r="C105" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B106" s="10">
+        <v>10000106</v>
+      </c>
+      <c r="C106" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="B107" s="10">
+        <v>10000107</v>
+      </c>
+      <c r="C107" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="B108" s="10">
+        <v>10000108</v>
+      </c>
+      <c r="C108" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="B109" s="10">
+        <v>10000109</v>
+      </c>
+      <c r="C109" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="B110" s="10">
+        <v>10000110</v>
+      </c>
+      <c r="C110" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="B111" s="10">
+        <v>10000111</v>
+      </c>
+      <c r="C111" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="B112" s="10">
+        <v>10000112</v>
+      </c>
+      <c r="C112" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B113" s="10">
+        <v>10000113</v>
+      </c>
+      <c r="C113" s="10">
+        <v>330304010</v>
+      </c>
+      <c r="D113" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B114" s="10">
+        <v>10000114</v>
+      </c>
+      <c r="C114" s="10">
+        <v>330304008</v>
+      </c>
+      <c r="D114" s="9" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="B115" s="10">
+        <v>10000115</v>
+      </c>
+      <c r="C115" s="10">
+        <v>330304008</v>
+      </c>
+      <c r="D115" s="9" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="B116" s="10">
+        <v>10000116</v>
+      </c>
+      <c r="C116" s="10">
+        <v>330304008</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="B117" s="10">
+        <v>10000117</v>
+      </c>
+      <c r="C117" s="10">
+        <v>330304008</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="B118" s="10">
+        <v>10000118</v>
+      </c>
+      <c r="C118" s="10">
+        <v>330304008</v>
+      </c>
+      <c r="D118" s="9" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B119" s="10">
+        <v>10000119</v>
+      </c>
+      <c r="C119" s="10">
+        <v>330304008</v>
+      </c>
+      <c r="D119" s="9" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="B120" s="10">
+        <v>10000120</v>
+      </c>
+      <c r="C120" s="10">
+        <v>330304008</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="B121" s="10">
+        <v>10000121</v>
+      </c>
+      <c r="C121" s="10">
+        <v>330304008</v>
+      </c>
+      <c r="D121" s="9" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B122" s="10">
+        <v>10000122</v>
+      </c>
+      <c r="C122" s="10">
+        <v>330304008</v>
+      </c>
+      <c r="D122" s="9" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="B123" s="10">
+        <v>10000123</v>
+      </c>
+      <c r="C123" s="10">
+        <v>330304008</v>
+      </c>
+      <c r="D123" s="9" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="B124" s="10">
+        <v>10000124</v>
+      </c>
+      <c r="C124" s="10">
+        <v>330304008</v>
+      </c>
+      <c r="D124" s="9" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="B125" s="10">
+        <v>10000125</v>
+      </c>
+      <c r="C125" s="10">
+        <v>330304008</v>
+      </c>
+      <c r="D125" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="B126" s="10">
+        <v>10000126</v>
+      </c>
+      <c r="C126" s="10">
+        <v>330304008</v>
+      </c>
+      <c r="D126" s="9" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="B127" s="10">
+        <v>10000127</v>
+      </c>
+      <c r="C127" s="10">
+        <v>330304008</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="B128" s="10">
+        <v>10000128</v>
+      </c>
+      <c r="C128" s="10">
+        <v>330304008</v>
+      </c>
+      <c r="D128" s="9" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B129" s="10">
+        <v>10000129</v>
+      </c>
+      <c r="C129" s="10">
+        <v>330304008</v>
+      </c>
+      <c r="D129" s="9" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="B130" s="10">
+        <v>10000130</v>
+      </c>
+      <c r="C130" s="10">
+        <v>330304007</v>
+      </c>
+      <c r="D130" s="9" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="B131" s="10">
+        <v>10000131</v>
+      </c>
+      <c r="C131" s="10">
+        <v>330304007</v>
+      </c>
+      <c r="D131" s="9" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="B132" s="10">
+        <v>10000132</v>
+      </c>
+      <c r="C132" s="10">
+        <v>330304007</v>
+      </c>
+      <c r="D132" s="9" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B133" s="10">
+        <v>10000133</v>
+      </c>
+      <c r="C133" s="10">
+        <v>330304007</v>
+      </c>
+      <c r="D133" s="9" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="B134" s="10">
+        <v>10000134</v>
+      </c>
+      <c r="C134" s="10">
+        <v>330304007</v>
+      </c>
+      <c r="D134" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="B135" s="10">
+        <v>10000135</v>
+      </c>
+      <c r="C135" s="10">
+        <v>330304007</v>
+      </c>
+      <c r="D135" s="9" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="B136" s="10">
+        <v>10000136</v>
+      </c>
+      <c r="C136" s="10">
+        <v>330304007</v>
+      </c>
+      <c r="D136" s="9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="B137" s="10">
+        <v>10000137</v>
+      </c>
+      <c r="C137" s="10">
+        <v>330304007</v>
+      </c>
+      <c r="D137" s="9" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="B138" s="10">
+        <v>10000138</v>
+      </c>
+      <c r="C138" s="10">
+        <v>330304007</v>
+      </c>
+      <c r="D138" s="9" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="B139" s="10">
+        <v>10000139</v>
+      </c>
+      <c r="C139" s="10">
+        <v>330304007</v>
+      </c>
+      <c r="D139" s="9" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="B140" s="10">
+        <v>10000140</v>
+      </c>
+      <c r="C140" s="10">
+        <v>330304007</v>
+      </c>
+      <c r="D140" s="9" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="B141" s="10">
+        <v>10000141</v>
+      </c>
+      <c r="C141" s="10">
+        <v>330304007</v>
+      </c>
+      <c r="D141" s="9" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="B142" s="10">
+        <v>10000142</v>
+      </c>
+      <c r="C142" s="10">
+        <v>330304007</v>
+      </c>
+      <c r="D142" s="9" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="B143" s="10">
+        <v>10000143</v>
+      </c>
+      <c r="C143" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D143" s="9" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="B144" s="10">
+        <v>10000144</v>
+      </c>
+      <c r="C144" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D144" s="9" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="B145" s="10">
+        <v>10000145</v>
+      </c>
+      <c r="C145" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D145" s="9" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="B146" s="10">
+        <v>10000146</v>
+      </c>
+      <c r="C146" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D146" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="B147" s="10">
+        <v>10000147</v>
+      </c>
+      <c r="C147" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D147" s="9" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="B148" s="10">
+        <v>10000148</v>
+      </c>
+      <c r="C148" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D148" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="B149" s="10">
+        <v>10000149</v>
+      </c>
+      <c r="C149" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D149" s="9" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="B150" s="10">
+        <v>10000150</v>
+      </c>
+      <c r="C150" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D150" s="9" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="B151" s="10">
+        <v>10000151</v>
+      </c>
+      <c r="C151" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D151" s="9" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="B152" s="10">
+        <v>10000152</v>
+      </c>
+      <c r="C152" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D152" s="9" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="B153" s="10">
+        <v>10000153</v>
+      </c>
+      <c r="C153" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D153" s="9" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="B154" s="10">
+        <v>10000154</v>
+      </c>
+      <c r="C154" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D154" s="9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B155" s="10">
+        <v>10000155</v>
+      </c>
+      <c r="C155" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D155" s="9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="B156" s="10">
+        <v>10000156</v>
+      </c>
+      <c r="C156" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D156" s="9" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="B157" s="10">
+        <v>10000157</v>
+      </c>
+      <c r="C157" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D157" s="9" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="B158" s="10">
+        <v>10000158</v>
+      </c>
+      <c r="C158" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D158" s="9" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="B159" s="10">
+        <v>10000159</v>
+      </c>
+      <c r="C159" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D159" s="9" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="B160" s="10">
+        <v>10000160</v>
+      </c>
+      <c r="C160" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D160" s="9" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="B161" s="10">
+        <v>10000161</v>
+      </c>
+      <c r="C161" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D161" s="9" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="B162" s="10">
+        <v>10000162</v>
+      </c>
+      <c r="C162" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D162" s="9" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="B163" s="10">
+        <v>10000163</v>
+      </c>
+      <c r="C163" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D163" s="9" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="B164" s="10">
+        <v>10000164</v>
+      </c>
+      <c r="C164" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D164" s="9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="B165" s="10">
+        <v>10000165</v>
+      </c>
+      <c r="C165" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D165" s="9" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="B166" s="10">
+        <v>10000166</v>
+      </c>
+      <c r="C166" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D166" s="9" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="B167" s="10">
+        <v>10000167</v>
+      </c>
+      <c r="C167" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D167" s="9" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="B168" s="10">
+        <v>10000168</v>
+      </c>
+      <c r="C168" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D168" s="9" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="B169" s="10">
+        <v>10000169</v>
+      </c>
+      <c r="C169" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D169" s="9" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
+      <c r="A170" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="B170" s="10">
+        <v>10000170</v>
+      </c>
+      <c r="C170" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D170" s="9" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="B171" s="10">
+        <v>10000171</v>
+      </c>
+      <c r="C171" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D171" s="9" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="B172" s="10">
+        <v>10000172</v>
+      </c>
+      <c r="C172" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D172" s="9" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="B173" s="10">
+        <v>10000173</v>
+      </c>
+      <c r="C173" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D173" s="9" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="B174" s="10">
+        <v>10000174</v>
+      </c>
+      <c r="C174" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D174" s="9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="B175" s="10">
+        <v>10000175</v>
+      </c>
+      <c r="C175" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D175" s="9" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="B176" s="10">
+        <v>10000176</v>
+      </c>
+      <c r="C176" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D176" s="9" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
+      <c r="A177" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="B177" s="10">
+        <v>10000177</v>
+      </c>
+      <c r="C177" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D177" s="9" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
+      <c r="A178" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="B178" s="10">
+        <v>10000178</v>
+      </c>
+      <c r="C178" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D178" s="9" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
+      <c r="A179" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="B179" s="10">
+        <v>10000179</v>
+      </c>
+      <c r="C179" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D179" s="9" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
+      <c r="A180" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="B180" s="10">
+        <v>10000180</v>
+      </c>
+      <c r="C180" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D180" s="9" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
+      <c r="A181" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="B181" s="10">
+        <v>10000181</v>
+      </c>
+      <c r="C181" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D181" s="9" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
+      <c r="A182" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="B182" s="10">
+        <v>10000182</v>
+      </c>
+      <c r="C182" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D182" s="9" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="B183" s="10">
+        <v>10000183</v>
+      </c>
+      <c r="C183" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D183" s="9" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
+      <c r="A184" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="B184" s="10">
+        <v>10000184</v>
+      </c>
+      <c r="C184" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D184" s="9" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4">
+      <c r="A185" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="B185" s="10">
+        <v>10000185</v>
+      </c>
+      <c r="C185" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D185" s="9" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
+      <c r="A186" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="B186" s="10">
+        <v>10000186</v>
+      </c>
+      <c r="C186" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D186" s="9" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4">
+      <c r="A187" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="B187" s="10">
+        <v>10000187</v>
+      </c>
+      <c r="C187" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D187" s="9" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
+      <c r="A188" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="B188" s="10">
+        <v>10000188</v>
+      </c>
+      <c r="C188" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D188" s="9" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
+      <c r="A189" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="B189" s="10">
+        <v>10000189</v>
+      </c>
+      <c r="C189" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D189" s="9" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
+      <c r="A190" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="B190" s="10">
+        <v>10000190</v>
+      </c>
+      <c r="C190" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D190" s="9" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="A191" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="B191" s="10">
+        <v>10000191</v>
+      </c>
+      <c r="C191" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D191" s="9" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
+      <c r="A192" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="B192" s="10">
+        <v>10000192</v>
+      </c>
+      <c r="C192" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D192" s="9" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4">
+      <c r="A193" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="B193" s="10">
+        <v>10000193</v>
+      </c>
+      <c r="C193" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D193" s="9" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="B194" s="10">
+        <v>10000194</v>
+      </c>
+      <c r="C194" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D194" s="9" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="B195" s="10">
+        <v>10000195</v>
+      </c>
+      <c r="C195" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D195" s="9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="B196" s="10">
+        <v>10000196</v>
+      </c>
+      <c r="C196" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D196" s="9" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="B197" s="10">
+        <v>10000197</v>
+      </c>
+      <c r="C197" s="10">
+        <v>330304012</v>
+      </c>
+      <c r="D197" s="9" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="B198" s="10">
+        <v>10000198</v>
+      </c>
+      <c r="C198" s="10">
+        <v>330304006</v>
+      </c>
+      <c r="D198" s="9" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="B199" s="10">
+        <v>10000199</v>
+      </c>
+      <c r="C199" s="10">
+        <v>330304006</v>
+      </c>
+      <c r="D199" s="9" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="B200" s="10">
+        <v>10000200</v>
+      </c>
+      <c r="C200" s="10">
+        <v>330304006</v>
+      </c>
+      <c r="D200" s="9" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="B201" s="10">
+        <v>10000201</v>
+      </c>
+      <c r="C201" s="10">
+        <v>330304006</v>
+      </c>
+      <c r="D201" s="9" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="B202" s="10">
+        <v>10000202</v>
+      </c>
+      <c r="C202" s="10">
+        <v>330304006</v>
+      </c>
+      <c r="D202" s="9" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="B203" s="10">
+        <v>10000203</v>
+      </c>
+      <c r="C203" s="10">
+        <v>330304006</v>
+      </c>
+      <c r="D203" s="9" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="B204" s="10">
+        <v>10000204</v>
+      </c>
+      <c r="C204" s="10">
+        <v>330304006</v>
+      </c>
+      <c r="D204" s="9" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="B205" s="10">
+        <v>10000205</v>
+      </c>
+      <c r="C205" s="10">
+        <v>330304006</v>
+      </c>
+      <c r="D205" s="9" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="B206" s="10">
+        <v>10000206</v>
+      </c>
+      <c r="C206" s="10">
+        <v>330304006</v>
+      </c>
+      <c r="D206" s="9" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="B207" s="10">
+        <v>10000207</v>
+      </c>
+      <c r="C207" s="10">
+        <v>330304006</v>
+      </c>
+      <c r="D207" s="9" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="B208" s="10">
+        <v>10000208</v>
+      </c>
+      <c r="C208" s="10">
+        <v>330304006</v>
+      </c>
+      <c r="D208" s="9" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="B209" s="10">
+        <v>10000209</v>
+      </c>
+      <c r="C209" s="10">
+        <v>330304006</v>
+      </c>
+      <c r="D209" s="9" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="B210" s="10">
+        <v>10000210</v>
+      </c>
+      <c r="C210" s="10">
+        <v>330304006</v>
+      </c>
+      <c r="D210" s="9" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="B211" s="10">
+        <v>10000211</v>
+      </c>
+      <c r="C211" s="10">
+        <v>330304006</v>
+      </c>
+      <c r="D211" s="9" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="B212" s="10">
+        <v>10000212</v>
+      </c>
+      <c r="C212" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D212" s="9" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="B213" s="10">
+        <v>10000213</v>
+      </c>
+      <c r="C213" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D213" s="9" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="B214" s="10">
+        <v>10000214</v>
+      </c>
+      <c r="C214" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D214" s="9" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B215" s="10">
+        <v>10000215</v>
+      </c>
+      <c r="C215" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D215" s="9" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="B216" s="10">
+        <v>10000216</v>
+      </c>
+      <c r="C216" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D216" s="9" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="B217" s="10">
+        <v>10000217</v>
+      </c>
+      <c r="C217" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D217" s="9" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="B218" s="10">
+        <v>10000218</v>
+      </c>
+      <c r="C218" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D218" s="9" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="B219" s="10">
+        <v>10000219</v>
+      </c>
+      <c r="C219" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D219" s="9" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="B220" s="10">
+        <v>10000220</v>
+      </c>
+      <c r="C220" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D220" s="9" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="B221" s="10">
+        <v>10000221</v>
+      </c>
+      <c r="C221" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D221" s="9" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="B222" s="10">
+        <v>10000222</v>
+      </c>
+      <c r="C222" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D222" s="9" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="B223" s="10">
+        <v>10000223</v>
+      </c>
+      <c r="C223" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D223" s="9" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="B224" s="10">
+        <v>10000224</v>
+      </c>
+      <c r="C224" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D224" s="9" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="B225" s="10">
+        <v>10000225</v>
+      </c>
+      <c r="C225" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D225" s="9" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="B226" s="10">
+        <v>10000226</v>
+      </c>
+      <c r="C226" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D226" s="9" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="B227" s="10">
+        <v>10000227</v>
+      </c>
+      <c r="C227" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D227" s="9" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="B228" s="10">
+        <v>10000228</v>
+      </c>
+      <c r="C228" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D228" s="9" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="B229" s="10">
+        <v>10000229</v>
+      </c>
+      <c r="C229" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D229" s="9" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="B230" s="10">
+        <v>10000230</v>
+      </c>
+      <c r="C230" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D230" s="9" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="B231" s="10">
+        <v>10000231</v>
+      </c>
+      <c r="C231" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D231" s="9" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="B232" s="10">
+        <v>10000232</v>
+      </c>
+      <c r="C232" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D232" s="9" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="B233" s="10">
+        <v>10000233</v>
+      </c>
+      <c r="C233" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D233" s="9" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="B234" s="10">
+        <v>10000234</v>
+      </c>
+      <c r="C234" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D234" s="9" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="B235" s="10">
+        <v>10000235</v>
+      </c>
+      <c r="C235" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D235" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="B236" s="10">
+        <v>10000236</v>
+      </c>
+      <c r="C236" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D236" s="9" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="B237" s="10">
+        <v>10000237</v>
+      </c>
+      <c r="C237" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D237" s="9" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="B238" s="10">
+        <v>10000238</v>
+      </c>
+      <c r="C238" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D238" s="9" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="B239" s="10">
+        <v>10000239</v>
+      </c>
+      <c r="C239" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D239" s="9" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="B240" s="10">
+        <v>10000240</v>
+      </c>
+      <c r="C240" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D240" s="9" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="B241" s="10">
+        <v>10000241</v>
+      </c>
+      <c r="C241" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D241" s="9" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="B242" s="10">
+        <v>10000242</v>
+      </c>
+      <c r="C242" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D242" s="9" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="B243" s="10">
+        <v>10000243</v>
+      </c>
+      <c r="C243" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D243" s="9" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="B244" s="10">
+        <v>10000244</v>
+      </c>
+      <c r="C244" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D244" s="9" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="B245" s="10">
+        <v>10000245</v>
+      </c>
+      <c r="C245" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D245" s="9" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="B246" s="10">
+        <v>10000246</v>
+      </c>
+      <c r="C246" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D246" s="9" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="B247" s="10">
+        <v>10000247</v>
+      </c>
+      <c r="C247" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D247" s="9" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="B248" s="10">
+        <v>10000248</v>
+      </c>
+      <c r="C248" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D248" s="9" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="B249" s="10">
+        <v>10000249</v>
+      </c>
+      <c r="C249" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D249" s="9" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="B250" s="10">
+        <v>10000250</v>
+      </c>
+      <c r="C250" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D250" s="9" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="B251" s="10">
+        <v>10000251</v>
+      </c>
+      <c r="C251" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D251" s="9" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="B252" s="10">
+        <v>10000252</v>
+      </c>
+      <c r="C252" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D252" s="9" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="B253" s="10">
+        <v>10000253</v>
+      </c>
+      <c r="C253" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D253" s="9" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="B254" s="10">
+        <v>10000254</v>
+      </c>
+      <c r="C254" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D254" s="9" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="B255" s="10">
+        <v>10000255</v>
+      </c>
+      <c r="C255" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D255" s="9" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="B256" s="10">
+        <v>10000256</v>
+      </c>
+      <c r="C256" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D256" s="9" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="B257" s="10">
+        <v>10000257</v>
+      </c>
+      <c r="C257" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D257" s="9" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="B258" s="10">
+        <v>10000258</v>
+      </c>
+      <c r="C258" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D258" s="9" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="B259" s="10">
+        <v>10000259</v>
+      </c>
+      <c r="C259" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D259" s="9" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="B260" s="10">
+        <v>10000260</v>
+      </c>
+      <c r="C260" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D260" s="9" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="B261" s="10">
+        <v>10000261</v>
+      </c>
+      <c r="C261" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D261" s="9" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="B262" s="10">
+        <v>10000262</v>
+      </c>
+      <c r="C262" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D262" s="9" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="B263" s="10">
+        <v>10000263</v>
+      </c>
+      <c r="C263" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D263" s="9" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="B264" s="10">
+        <v>10000264</v>
+      </c>
+      <c r="C264" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D264" s="9" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="B265" s="10">
+        <v>10000265</v>
+      </c>
+      <c r="C265" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D265" s="9" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="B266" s="10">
+        <v>10000266</v>
+      </c>
+      <c r="C266" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D266" s="9" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="B267" s="10">
+        <v>10000267</v>
+      </c>
+      <c r="C267" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D267" s="9" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="B268" s="10">
+        <v>10000268</v>
+      </c>
+      <c r="C268" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D268" s="9" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="B269" s="10">
+        <v>10000269</v>
+      </c>
+      <c r="C269" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D269" s="9" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="B270" s="10">
+        <v>10000270</v>
+      </c>
+      <c r="C270" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D270" s="9" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="B271" s="10">
+        <v>10000271</v>
+      </c>
+      <c r="C271" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D271" s="9" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="B272" s="10">
+        <v>10000272</v>
+      </c>
+      <c r="C272" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D272" s="9" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="B273" s="10">
+        <v>10000273</v>
+      </c>
+      <c r="C273" s="10">
+        <v>330304108</v>
+      </c>
+      <c r="D273" s="9" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="B274" s="10">
+        <v>10000274</v>
+      </c>
+      <c r="C274" s="10">
+        <v>330304002</v>
+      </c>
+      <c r="D274" s="9" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="B275" s="10">
+        <v>10000275</v>
+      </c>
+      <c r="C275" s="10">
+        <v>330304001</v>
+      </c>
+      <c r="D275" s="9" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="B276" s="10">
+        <v>10000276</v>
+      </c>
+      <c r="C276" s="10">
+        <v>330304003</v>
+      </c>
+      <c r="D276" s="9" t="s">
+        <v>533</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="DTvAxXTBxPYpzbv4fBuCum32MGDCvQlFDG6rWl2a7VQ4kX49JBlBnDjOA1g+iTq0zn1mrcrlvgGaX6AA7F3utw==" saltValue="6lorVOAfoezwkHdOFY0lWQ==" spinCount="100000" sheet="1" objects="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:BK13"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="63" max="63" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="8" customFormat="1" spans="1:63">
+      <c r="A1" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="2" s="8" customFormat="1" spans="1:63">
+      <c r="A2" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="V2" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="W2" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="X2" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="Y2" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="Z2" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="AA2" s="8" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="3" s="8" customFormat="1" spans="1:63">
+      <c r="A3" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="4" s="8" customFormat="1" spans="1:63">
+      <c r="A4" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" s="8" customFormat="1" spans="1:63">
+      <c r="A5" s="8" t="s">
+        <v>538</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" s="8" customFormat="1" spans="1:63">
+      <c r="A6" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="7" s="8" customFormat="1" spans="1:63">
+      <c r="A7" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" s="8" customFormat="1" spans="1:63">
+      <c r="A8" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="9" s="8" customFormat="1" spans="1:63">
+      <c r="A9" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" s="8" customFormat="1" spans="1:63">
+      <c r="A10" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="R10" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="S10" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="T10" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="U10" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="V10" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="W10" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="X10" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="Y10" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z10" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="AA10" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB10" s="8" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="11" s="8" customFormat="1" spans="1:63">
+      <c r="A11" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" s="8" customFormat="1" spans="1:63">
+      <c r="A12" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="S12" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="T12" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="U12" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="V12" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="W12" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="X12" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="Y12" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="Z12" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="AA12" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="AB12" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="AC12" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="AD12" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="AE12" s="8" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="13" s="8" customFormat="1" spans="1:63">
+      <c r="A13" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="R13" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="S13" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="T13" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="U13" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="V13" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="W13" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="X13" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="Y13" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="Z13" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="AA13" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="AB13" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="AC13" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="AD13" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="AE13" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="AF13" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="AG13" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="AH13" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="AI13" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="AJ13" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="AK13" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="AL13" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="AM13" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="AN13" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="AO13" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="AP13" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="AQ13" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="AR13" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="AS13" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="AT13" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="AU13" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="AV13" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="AW13" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="AX13" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="AY13" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="AZ13" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="BA13" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="BB13" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="BC13" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="BD13" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="BE13" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="BF13" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="BG13" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="BH13" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="BI13" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="BJ13" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="BK13" s="8" t="s">
+        <v>526</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="OLFG68X9RWT/7dnTKD1O7q0ai7wxJoyWQkPZEyNe2rAMpzGXENKiZvah47BGMrbkCZjdCl3HlxqMva0tB5oS2A==" saltValue="Dpae/efUg3iA3zFf3krUWg==" spinCount="100000" sheet="1" objects="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="13.8888888888889" style="6" customWidth="1"/>
+    <col min="2" max="2" width="14.3333333333333" style="6" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="B1" s="7">
+        <v>330304001</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="B2" s="7">
+        <v>330304002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="B3" s="7">
+        <v>330304003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="B4" s="7">
+        <v>330304004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="B5" s="7">
+        <v>330304005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="B6" s="7">
+        <v>330304006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="B7" s="7">
+        <v>330304007</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="B8" s="7">
+        <v>330304008</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="B9" s="7">
+        <v>330304009</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="B10" s="7">
+        <v>330304010</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="B11" s="7">
+        <v>330304011</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="B12" s="7">
+        <v>330304012</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="B13" s="7">
+        <v>330304108</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="6GFpGLXW4SMxyHycOlPIrLkvZFL9k2QO7l3uM5HlkO+84bbUojGCiNv9oxiuHAS9Hw42ZjSy95dbCK3sCZm7cQ==" saltValue="H2k6jU4sAa7denTSds2D0g==" spinCount="100000" sheet="1" objects="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="1"/>
+  <sheetData>
+    <row r="1" spans="1:2">
       <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:4">
-      <c r="B2" s="3" t="s">
-        <v>4</v>
+        <v>547</v>
+      </c>
+      <c r="B1" s="5">
+        <v>10000006</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="B2" s="5">
+        <v>10000007</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
-      <formula1>"组员,组长"</formula1>
+  <sheetProtection algorithmName="SHA-512" hashValue="Gd7ScQpSWjKQonBoFJzD1mtg7EYb4IwfeI1ynb52nh38Aa4UwJv/uhjUHrnL3IP4spj/zWcqQRkpr5+jPSryvg==" saltValue="9r3f9aOg71D0Sw+cmUF6Rg==" spinCount="100000" sheet="1" objects="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet5"/>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="25" customHeight="1" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="22.2222222222222" style="2" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="21.8888888888889" style="2" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="28.3333333333333" style="3" customWidth="1"/>
+    <col min="5" max="5" width="25.5555555555556" style="3" customWidth="1"/>
+    <col min="6" max="6" width="11.6666666666667" style="3" customWidth="1"/>
+    <col min="7" max="7" width="19.2222222222222" style="3" customWidth="1"/>
+    <col min="8" max="8" width="105.444444444444" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13" style="2" customWidth="1"/>
+    <col min="10" max="10" width="16.2222222222222" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="8.88888888888889" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="32" customHeight="1" spans="1:8">
+      <c r="A1" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>556</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F$1:F$1048576">
+      <formula1>role!$A$1:$A$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G$1:G$1048576">
+      <formula1>town!$A$1:$A$13</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576">
+      <formula1>INDIRECT(G2)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<allowEditUser xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" hasInvisiblePropRange="0">
+  <rangeList sheetStid="1" master="" otherUserPermission="visible"/>
+  <rangeList sheetStid="2" master="" otherUserPermission="visible"/>
+  <rangeList sheetStid="3" master="" otherUserPermission="visible"/>
+  <rangeList sheetStid="4" master="" otherUserPermission="visible"/>
+  <rangeList sheetStid="5" master="" otherUserPermission="visible"/>
+</allowEditUser>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A5607D9-04D2-4DE1-AC0E-A7772F01BC71}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>